--- a/DataTables/剧情大纲.xlsx
+++ b/DataTables/剧情大纲.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{124395C8-0411-405B-AE02-0180CA53A338}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E31FF70E-63A7-45DD-A59A-82B89C13D2DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="时间线" sheetId="1" r:id="rId1"/>

--- a/DataTables/剧情大纲.xlsx
+++ b/DataTables/剧情大纲.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E31FF70E-63A7-45DD-A59A-82B89C13D2DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{771E3AE2-2A92-49AB-8ECA-A34A728231B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="时间线" sheetId="1" r:id="rId1"/>
@@ -895,13 +895,13 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="6"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -945,13 +945,13 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -960,7 +960,7 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1043,7 +1043,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1322,17 +1322,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="5.265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.25" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.46484375" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.3984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.375" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="18">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1349,7 +1349,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="18">
+    <row r="2" spans="1:5">
       <c r="B2" s="2" t="s">
         <v>3</v>
       </c>
@@ -1363,7 +1363,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="18">
+    <row r="3" spans="1:5">
       <c r="B3" s="2" t="s">
         <v>4</v>
       </c>
@@ -1377,7 +1377,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="18">
+    <row r="4" spans="1:5">
       <c r="B4" s="2" t="s">
         <v>7</v>
       </c>
@@ -1391,7 +1391,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="18">
+    <row r="5" spans="1:5">
       <c r="A5" s="2" t="s">
         <v>9</v>
       </c>
@@ -1408,7 +1408,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="18">
+    <row r="6" spans="1:5">
       <c r="B6" s="2" t="s">
         <v>17</v>
       </c>
@@ -1431,19 +1431,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD551C76-47E1-4A91-9FB6-46DD09A2A3A3}">
   <dimension ref="A1:H20"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="4.46484375" style="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.1328125" style="9" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.265625" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.5" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.125" style="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.25" style="9" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9" style="9"/>
-    <col min="5" max="5" width="5.265625" style="9" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="5.46484375" style="9" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.265625" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.25" style="9" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="5.5" style="9" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.25" style="9" bestFit="1" customWidth="1"/>
     <col min="9" max="16384" width="9" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="18">
+    <row r="1" spans="1:8">
       <c r="A1" s="8" t="s">
         <v>134</v>
       </c>
@@ -1469,7 +1469,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="18">
+    <row r="2" spans="1:8">
       <c r="A2" s="16" t="s">
         <v>132</v>
       </c>
@@ -1479,11 +1479,8 @@
       <c r="E2" s="9">
         <v>3</v>
       </c>
-      <c r="H2" s="9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="18">
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" s="16" t="s">
         <v>124</v>
       </c>
@@ -1494,7 +1491,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="18">
+    <row r="4" spans="1:8">
       <c r="A4" s="16" t="s">
         <v>132</v>
       </c>
@@ -1509,7 +1506,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="18">
+    <row r="5" spans="1:8">
       <c r="A5" s="16" t="s">
         <v>23</v>
       </c>
@@ -1520,7 +1517,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="18">
+    <row r="6" spans="1:8">
       <c r="A6" s="16" t="s">
         <v>125</v>
       </c>
@@ -1531,7 +1528,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="18">
+    <row r="7" spans="1:8">
       <c r="A7" s="16" t="s">
         <v>126</v>
       </c>
@@ -1542,53 +1539,50 @@
         <v>44</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="18">
+    <row r="8" spans="1:8">
       <c r="A8" s="16" t="s">
+        <v>145</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="C8" s="8"/>
+      <c r="D8" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="E8" s="9">
+        <v>3</v>
+      </c>
+      <c r="H8" s="9">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B9" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="C8" s="8">
+      <c r="C9" s="8">
         <v>55</v>
       </c>
-      <c r="G8" s="9">
+      <c r="G9" s="9">
         <v>1000</v>
       </c>
-      <c r="H8" s="9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="18">
-      <c r="A9" s="16" t="s">
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B10" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="C9" s="8">
+      <c r="C10" s="8">
         <v>76</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="18">
-      <c r="A10" s="16" t="s">
-        <v>145</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>146</v>
-      </c>
-      <c r="C10" s="8"/>
-      <c r="D10" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="E10" s="9">
-        <v>1</v>
-      </c>
-      <c r="H10" s="9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="18">
+    <row r="11" spans="1:8">
       <c r="A11" s="16" t="s">
         <v>25</v>
       </c>
@@ -1599,7 +1593,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="18">
+    <row r="12" spans="1:8">
       <c r="A12" s="16" t="s">
         <v>127</v>
       </c>
@@ -1613,7 +1607,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="18">
+    <row r="13" spans="1:8">
       <c r="A13" s="16" t="s">
         <v>136</v>
       </c>
@@ -1625,7 +1619,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="18">
+    <row r="14" spans="1:8">
       <c r="A14" s="16" t="s">
         <v>128</v>
       </c>
@@ -1642,7 +1636,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="18">
+    <row r="15" spans="1:8">
       <c r="A15" s="16" t="s">
         <v>138</v>
       </c>
@@ -1657,7 +1651,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="18">
+    <row r="16" spans="1:8">
       <c r="A16" s="16" t="s">
         <v>131</v>
       </c>
@@ -1671,16 +1665,16 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:1" ht="18">
+    <row r="17" spans="1:1">
       <c r="A17" s="16"/>
     </row>
-    <row r="18" spans="1:1" ht="18">
+    <row r="18" spans="1:1">
       <c r="A18" s="16"/>
     </row>
-    <row r="19" spans="1:1" ht="18">
+    <row r="19" spans="1:1">
       <c r="A19" s="16"/>
     </row>
-    <row r="20" spans="1:1" ht="18">
+    <row r="20" spans="1:1">
       <c r="A20" s="16"/>
     </row>
   </sheetData>
@@ -1692,16 +1686,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B3CE6F5-4C98-4917-9759-7DA81A6E4796}">
   <dimension ref="A1:I23"/>
-  <sheetFormatPr defaultRowHeight="13.9"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="7" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.1328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.1328125" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.125" style="9" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="9" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="21.3984375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="18">
+    <row r="1" spans="1:9">
       <c r="A1" s="6" t="s">
         <v>69</v>
       </c>
@@ -1724,7 +1718,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="18">
+    <row r="2" spans="1:9">
       <c r="A2" s="6" t="s">
         <v>23</v>
       </c>
@@ -1738,7 +1732,7 @@
       <c r="G2" s="4"/>
       <c r="I2" s="4"/>
     </row>
-    <row r="3" spans="1:9" ht="18">
+    <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
         <v>24</v>
       </c>
@@ -1755,7 +1749,7 @@
       <c r="G3" s="4"/>
       <c r="I3" s="4"/>
     </row>
-    <row r="4" spans="1:9" ht="18">
+    <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
         <v>25</v>
       </c>
@@ -1769,7 +1763,7 @@
       <c r="G4" s="4"/>
       <c r="I4" s="4"/>
     </row>
-    <row r="5" spans="1:9" ht="18">
+    <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
         <v>26</v>
       </c>
@@ -1783,7 +1777,7 @@
       <c r="G5" s="4"/>
       <c r="I5" s="5"/>
     </row>
-    <row r="6" spans="1:9" ht="18">
+    <row r="6" spans="1:9">
       <c r="A6" s="6" t="s">
         <v>40</v>
       </c>
@@ -1796,7 +1790,7 @@
       <c r="D6" s="8"/>
       <c r="G6" s="4"/>
     </row>
-    <row r="7" spans="1:9" ht="18">
+    <row r="7" spans="1:9">
       <c r="A7" s="6" t="s">
         <v>41</v>
       </c>
@@ -1809,7 +1803,7 @@
       <c r="G7" s="4"/>
       <c r="I7" s="4"/>
     </row>
-    <row r="8" spans="1:9" ht="18">
+    <row r="8" spans="1:9">
       <c r="A8" s="6" t="s">
         <v>42</v>
       </c>
@@ -1822,7 +1816,7 @@
       <c r="G8" s="4"/>
       <c r="I8" s="4"/>
     </row>
-    <row r="9" spans="1:9" ht="18">
+    <row r="9" spans="1:9">
       <c r="A9" s="6" t="s">
         <v>43</v>
       </c>
@@ -1835,7 +1829,7 @@
       <c r="G9" s="4"/>
       <c r="I9" s="4"/>
     </row>
-    <row r="10" spans="1:9" ht="18">
+    <row r="10" spans="1:9">
       <c r="A10" s="6" t="s">
         <v>44</v>
       </c>
@@ -1848,7 +1842,7 @@
       <c r="G10" s="4"/>
       <c r="I10" s="5"/>
     </row>
-    <row r="11" spans="1:9" ht="18">
+    <row r="11" spans="1:9">
       <c r="A11" s="6" t="s">
         <v>27</v>
       </c>
@@ -1864,7 +1858,7 @@
       <c r="G11" s="4"/>
       <c r="I11" s="4"/>
     </row>
-    <row r="12" spans="1:9" ht="18">
+    <row r="12" spans="1:9">
       <c r="A12" s="6" t="s">
         <v>55</v>
       </c>
@@ -1878,7 +1872,7 @@
       <c r="G12" s="4"/>
       <c r="I12" s="4"/>
     </row>
-    <row r="13" spans="1:9" ht="18">
+    <row r="13" spans="1:9">
       <c r="A13" s="6" t="s">
         <v>56</v>
       </c>
@@ -1891,7 +1885,7 @@
       </c>
       <c r="I13" s="4"/>
     </row>
-    <row r="14" spans="1:9" ht="18">
+    <row r="14" spans="1:9">
       <c r="A14" s="6" t="s">
         <v>28</v>
       </c>
@@ -1906,7 +1900,7 @@
       </c>
       <c r="I14" s="4"/>
     </row>
-    <row r="15" spans="1:9" ht="18">
+    <row r="15" spans="1:9">
       <c r="A15" s="6" t="s">
         <v>57</v>
       </c>
@@ -1917,7 +1911,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="18">
+    <row r="16" spans="1:9">
       <c r="A16" s="6" t="s">
         <v>58</v>
       </c>
@@ -1929,7 +1923,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="18">
+    <row r="17" spans="1:6">
       <c r="A17" s="6" t="s">
         <v>59</v>
       </c>
@@ -1940,7 +1934,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="18">
+    <row r="18" spans="1:6">
       <c r="A18" s="6" t="s">
         <v>60</v>
       </c>
@@ -1954,20 +1948,20 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="18">
+    <row r="19" spans="1:6">
       <c r="A19" s="6"/>
       <c r="B19" s="4"/>
     </row>
-    <row r="20" spans="1:6" ht="18">
+    <row r="20" spans="1:6">
       <c r="A20" s="6"/>
     </row>
-    <row r="21" spans="1:6" ht="18">
+    <row r="21" spans="1:6">
       <c r="A21" s="6"/>
     </row>
-    <row r="22" spans="1:6" ht="18">
+    <row r="22" spans="1:6">
       <c r="A22" s="6"/>
     </row>
-    <row r="23" spans="1:6" ht="18">
+    <row r="23" spans="1:6">
       <c r="A23" s="6"/>
     </row>
   </sheetData>
@@ -1979,9 +1973,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35DA3626-9D35-4B08-8B66-BF275758C0A6}">
   <dimension ref="A1:K12"/>
-  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="7.1328125" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.125" style="8" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13" style="8" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="9" style="8" bestFit="1" customWidth="1"/>
   </cols>
@@ -2105,10 +2099,10 @@
   <dimension ref="A1:I17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="12.86328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.86328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.875" style="4" bestFit="1" customWidth="1"/>
     <col min="3" max="6" width="9" style="4"/>
-    <col min="7" max="7" width="8.59765625" style="4" customWidth="1"/>
+    <col min="7" max="7" width="8.625" style="4" customWidth="1"/>
     <col min="8" max="8" width="9" style="11"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
@@ -2351,9 +2345,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA86077C-61A9-404C-B3A5-652B97F71E5C}">
   <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultRowHeight="13.9"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
-    <row r="1" spans="1:6" ht="18">
+    <row r="1" spans="1:6">
       <c r="A1" s="14" t="s">
         <v>108</v>
       </c>
@@ -2367,7 +2361,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="18">
+    <row r="2" spans="1:6">
       <c r="A2" s="14" t="s">
         <v>109</v>
       </c>
@@ -2381,7 +2375,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="18">
+    <row r="3" spans="1:6">
       <c r="A3" s="15" t="s">
         <v>110</v>
       </c>
@@ -2392,7 +2386,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="18">
+    <row r="4" spans="1:6">
       <c r="A4" s="15" t="s">
         <v>111</v>
       </c>

--- a/DataTables/剧情大纲.xlsx
+++ b/DataTables/剧情大纲.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{771E3AE2-2A92-49AB-8ECA-A34A728231B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50C9E81D-7C40-4C44-93EF-023EEF401B1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="153">
   <si>
     <t>嘉靖</t>
     <phoneticPr fontId="1"/>
@@ -885,6 +885,14 @@
   </si>
   <si>
     <t>谢飞燕肺阴虚</t>
+  </si>
+  <si>
+    <t>028</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>痰迷心窍</t>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -1430,7 +1438,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD551C76-47E1-4A91-9FB6-46DD09A2A3A3}">
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="4.5" style="9" bestFit="1" customWidth="1"/>
@@ -1572,110 +1580,121 @@
       </c>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>32</v>
+      <c r="A10" s="18" t="s">
+        <v>151</v>
+      </c>
+      <c r="B10" s="17" t="s">
+        <v>152</v>
       </c>
       <c r="C10" s="8">
-        <v>76</v>
+        <v>62</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="16" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C11" s="8">
-        <v>92</v>
+        <v>76</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="16" t="s">
-        <v>127</v>
+        <v>25</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="C12" s="8">
-        <v>98</v>
-      </c>
-      <c r="F12" s="9">
-        <v>2000</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="16" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>137</v>
-      </c>
-      <c r="C13" s="8"/>
-      <c r="E13" s="9">
-        <v>26</v>
+        <v>21</v>
+      </c>
+      <c r="C13" s="8">
+        <v>98</v>
+      </c>
+      <c r="F13" s="9">
+        <v>2000</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="16" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="C14" s="8">
-        <v>105</v>
-      </c>
-      <c r="D14" s="16" t="s">
-        <v>139</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="C14" s="8"/>
       <c r="E14" s="9">
-        <v>1</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="16" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>130</v>
-      </c>
-      <c r="C15" s="8"/>
+        <v>22</v>
+      </c>
+      <c r="C15" s="8">
+        <v>105</v>
+      </c>
       <c r="D15" s="16" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="E15" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="16" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>16</v>
-      </c>
+        <v>130</v>
+      </c>
+      <c r="C16" s="8"/>
       <c r="D16" s="16" t="s">
-        <v>60</v>
+        <v>128</v>
       </c>
       <c r="E16" s="9">
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:1">
-      <c r="A17" s="16"/>
-    </row>
-    <row r="18" spans="1:1">
+    <row r="17" spans="1:5">
+      <c r="A17" s="16" t="s">
+        <v>131</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D17" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="E17" s="9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
       <c r="A18" s="16"/>
     </row>
-    <row r="19" spans="1:1">
+    <row r="19" spans="1:5">
       <c r="A19" s="16"/>
     </row>
-    <row r="20" spans="1:1">
+    <row r="20" spans="1:5">
       <c r="A20" s="16"/>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="16"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>

--- a/DataTables/剧情大纲.xlsx
+++ b/DataTables/剧情大纲.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50C9E81D-7C40-4C44-93EF-023EEF401B1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F2529DA-F144-495D-8E72-6972A76759B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="时间线" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,6 @@
     <sheet name="赈灾药材案" sheetId="2" r:id="rId3"/>
     <sheet name="支线剧情" sheetId="3" r:id="rId4"/>
     <sheet name="收入" sheetId="4" r:id="rId5"/>
-    <sheet name="音乐" sheetId="5" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="144">
   <si>
     <t>嘉靖</t>
     <phoneticPr fontId="1"/>
@@ -697,20 +696,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>春：竹笛《春到湘江》</t>
-  </si>
-  <si>
-    <t>夏：琵琶《月儿高》</t>
-  </si>
-  <si>
-    <t>秋：洞箫《平沙落雁》</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>冬：古琴《梅花三弄》</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
     <t>田租</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -735,42 +720,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>鸟叫</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>蟋蟀青蛙</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>猫头鹰</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>乌鸦</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>树叶摩挲</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>寒风</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>小</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>大</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>蝉鸣</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
     <t>022</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -894,12 +843,28 @@
     <t>痰迷心窍</t>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>秋税</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>夏税</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>大暑</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>霜降</t>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -949,30 +914,6 @@
       <family val="2"/>
       <charset val="134"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="游ゴシック"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="游ゴシック"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="游ゴシック"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1009,7 +950,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1038,8 +979,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1453,13 +1392,13 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="8" t="s">
-        <v>134</v>
+        <v>121</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="D1" s="8" t="s">
         <v>72</v>
@@ -1468,94 +1407,94 @@
         <v>75</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>142</v>
+        <v>129</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>143</v>
+        <v>130</v>
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="16" t="s">
-        <v>132</v>
+      <c r="A2" s="14" t="s">
+        <v>119</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>133</v>
+        <v>120</v>
       </c>
       <c r="E2" s="9">
         <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="16" t="s">
-        <v>124</v>
+      <c r="A3" s="14" t="s">
+        <v>111</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>148</v>
+        <v>135</v>
       </c>
       <c r="C3" s="8">
         <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="16" t="s">
-        <v>132</v>
+      <c r="A4" s="14" t="s">
+        <v>119</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>140</v>
+        <v>127</v>
       </c>
       <c r="C4" s="8"/>
-      <c r="D4" s="16" t="s">
-        <v>124</v>
+      <c r="D4" s="14" t="s">
+        <v>111</v>
       </c>
       <c r="E4" s="9">
         <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="16" t="s">
+      <c r="A5" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="17" t="s">
-        <v>147</v>
+      <c r="B5" s="15" t="s">
+        <v>134</v>
       </c>
       <c r="C5" s="8">
         <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="16" t="s">
-        <v>125</v>
+      <c r="A6" s="14" t="s">
+        <v>112</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>149</v>
+        <v>136</v>
       </c>
       <c r="C6" s="8">
         <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="16" t="s">
-        <v>126</v>
+      <c r="A7" s="14" t="s">
+        <v>113</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>150</v>
+        <v>137</v>
       </c>
       <c r="C7" s="8">
         <v>44</v>
       </c>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" s="16" t="s">
-        <v>145</v>
+      <c r="A8" s="14" t="s">
+        <v>132</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>146</v>
+        <v>133</v>
       </c>
       <c r="C8" s="8"/>
-      <c r="D8" s="18" t="s">
+      <c r="D8" s="16" t="s">
         <v>26</v>
       </c>
       <c r="E8" s="9">
@@ -1566,7 +1505,7 @@
       </c>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="16" t="s">
+      <c r="A9" s="14" t="s">
         <v>24</v>
       </c>
       <c r="B9" s="8" t="s">
@@ -1580,18 +1519,18 @@
       </c>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10" s="18" t="s">
-        <v>151</v>
-      </c>
-      <c r="B10" s="17" t="s">
-        <v>152</v>
+      <c r="A10" s="16" t="s">
+        <v>138</v>
+      </c>
+      <c r="B10" s="15" t="s">
+        <v>139</v>
       </c>
       <c r="C10" s="8">
         <v>62</v>
       </c>
     </row>
     <row r="11" spans="1:8">
-      <c r="A11" s="16" t="s">
+      <c r="A11" s="14" t="s">
         <v>26</v>
       </c>
       <c r="B11" s="8" t="s">
@@ -1602,7 +1541,7 @@
       </c>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" s="16" t="s">
+      <c r="A12" s="14" t="s">
         <v>25</v>
       </c>
       <c r="B12" s="8" t="s">
@@ -1613,8 +1552,8 @@
       </c>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" s="16" t="s">
-        <v>127</v>
+      <c r="A13" s="14" t="s">
+        <v>114</v>
       </c>
       <c r="B13" s="8" t="s">
         <v>21</v>
@@ -1627,11 +1566,11 @@
       </c>
     </row>
     <row r="14" spans="1:8">
-      <c r="A14" s="16" t="s">
-        <v>136</v>
+      <c r="A14" s="14" t="s">
+        <v>123</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="C14" s="8"/>
       <c r="E14" s="9">
@@ -1639,8 +1578,8 @@
       </c>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15" s="16" t="s">
-        <v>128</v>
+      <c r="A15" s="14" t="s">
+        <v>115</v>
       </c>
       <c r="B15" s="8" t="s">
         <v>22</v>
@@ -1648,36 +1587,36 @@
       <c r="C15" s="8">
         <v>105</v>
       </c>
-      <c r="D15" s="16" t="s">
-        <v>139</v>
+      <c r="D15" s="14" t="s">
+        <v>126</v>
       </c>
       <c r="E15" s="9">
         <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" s="16" t="s">
-        <v>138</v>
+      <c r="A16" s="14" t="s">
+        <v>125</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>130</v>
+        <v>117</v>
       </c>
       <c r="C16" s="8"/>
-      <c r="D16" s="16" t="s">
-        <v>128</v>
+      <c r="D16" s="14" t="s">
+        <v>115</v>
       </c>
       <c r="E16" s="9">
         <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="16" t="s">
-        <v>131</v>
+      <c r="A17" s="14" t="s">
+        <v>118</v>
       </c>
       <c r="B17" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D17" s="16" t="s">
+      <c r="D17" s="14" t="s">
         <v>60</v>
       </c>
       <c r="E17" s="9">
@@ -1685,16 +1624,16 @@
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="16"/>
+      <c r="A18" s="14"/>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="16"/>
+      <c r="A19" s="14"/>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="16"/>
+      <c r="A20" s="14"/>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="16"/>
+      <c r="A21" s="14"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
@@ -1804,7 +1743,7 @@
         <v>35</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D6" s="8"/>
       <c r="G6" s="4"/>
@@ -2094,7 +2033,7 @@
     </row>
     <row r="9" spans="1:11">
       <c r="B9" s="8" t="s">
-        <v>129</v>
+        <v>116</v>
       </c>
       <c r="K9" s="8"/>
     </row>
@@ -2115,7 +2054,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00DA8846-409D-4B70-B280-9B5D3F94AB77}">
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="12.875" style="4" bestFit="1" customWidth="1"/>
@@ -2192,37 +2131,43 @@
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="B7" s="4">
-        <v>20000</v>
+        <v>108</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="C7" s="4">
+        <v>7000</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="B8" s="4">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9">
-      <c r="A10" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="B10" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="C8" s="4">
+        <v>14000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="B9" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="C10" s="4">
-        <v>1000</v>
+      <c r="C9" s="4">
+        <v>10000</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="4" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C11" s="4">
         <v>1000</v>
@@ -2230,93 +2175,87 @@
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>103</v>
+        <v>100</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>90</v>
       </c>
       <c r="C12" s="4">
-        <v>188</v>
-      </c>
-      <c r="D12" s="4">
-        <v>288</v>
-      </c>
-      <c r="E12" s="4">
-        <v>588</v>
-      </c>
-      <c r="F12" s="4">
-        <v>688</v>
-      </c>
-      <c r="G12" s="11">
-        <v>888</v>
-      </c>
-      <c r="H12" s="4">
-        <v>1888</v>
-      </c>
-      <c r="I12" s="4">
-        <v>2888</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="B13" s="11" t="s">
-        <v>92</v>
+        <v>102</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>103</v>
       </c>
       <c r="C13" s="4">
-        <v>300</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>91</v>
+        <v>188</v>
+      </c>
+      <c r="D13" s="4">
+        <v>288</v>
       </c>
       <c r="E13" s="4">
-        <v>1200</v>
+        <v>588</v>
+      </c>
+      <c r="F13" s="4">
+        <v>688</v>
+      </c>
+      <c r="G13" s="11">
+        <v>888</v>
+      </c>
+      <c r="H13" s="4">
+        <v>1888</v>
+      </c>
+      <c r="I13" s="4">
+        <v>2888</v>
       </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="4" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B14" s="11" t="s">
         <v>92</v>
       </c>
       <c r="C14" s="4">
-        <v>800</v>
+        <v>300</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>91</v>
       </c>
       <c r="E14" s="4">
-        <v>2000</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="D15" s="4">
-        <v>1000</v>
+        <v>104</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="C15" s="4">
+        <v>800</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>91</v>
       </c>
       <c r="E15" s="4">
         <v>2000</v>
       </c>
-      <c r="F15" s="4">
-        <v>3000</v>
-      </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="B16" s="11" t="s">
-        <v>99</v>
+        <v>97</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>96</v>
       </c>
       <c r="D16" s="4">
         <v>1000</v>
@@ -2330,13 +2269,10 @@
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>96</v>
+        <v>98</v>
+      </c>
+      <c r="B17" s="11" t="s">
+        <v>99</v>
       </c>
       <c r="D17" s="4">
         <v>1000</v>
@@ -2347,11 +2283,53 @@
       <c r="F17" s="4">
         <v>3000</v>
       </c>
-      <c r="G17" s="4">
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="D18" s="4">
+        <v>1000</v>
+      </c>
+      <c r="E18" s="4">
+        <v>2000</v>
+      </c>
+      <c r="F18" s="4">
+        <v>3000</v>
+      </c>
+      <c r="G18" s="4">
         <v>4000</v>
       </c>
-      <c r="H17" s="11">
+      <c r="H18" s="11">
         <v>5000</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="C19" s="4">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="C20" s="4">
+        <v>1000</v>
       </c>
     </row>
   </sheetData>
@@ -2359,65 +2337,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA86077C-61A9-404C-B3A5-652B97F71E5C}">
-  <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
-  <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" s="14" t="s">
-        <v>108</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2" s="14" t="s">
-        <v>109</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="15" t="s">
-        <v>110</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="15" t="s">
-        <v>111</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>120</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="8" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/DataTables/剧情大纲.xlsx
+++ b/DataTables/剧情大纲.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F2529DA-F144-495D-8E72-6972A76759B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{760D911C-C1D2-4507-9B87-E00B9CD90CBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="148">
   <si>
     <t>嘉靖</t>
     <phoneticPr fontId="1"/>
@@ -857,6 +857,22 @@
   </si>
   <si>
     <t>霜降</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>医书</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>每个节气</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>病家谢礼</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>妙手回春20%</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -950,7 +966,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -988,6 +1004,7 @@
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -2054,7 +2071,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00DA8846-409D-4B70-B280-9B5D3F94AB77}">
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:L23"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="12.875" style="4" bestFit="1" customWidth="1"/>
@@ -2065,7 +2082,7 @@
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:8">
       <c r="A1" s="12"/>
       <c r="B1" s="12" t="s">
         <v>76</v>
@@ -2074,7 +2091,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:8">
       <c r="A2" s="13" t="s">
         <v>77</v>
       </c>
@@ -2085,7 +2102,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:8">
       <c r="A3" s="12" t="s">
         <v>78</v>
       </c>
@@ -2096,7 +2113,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:8">
       <c r="A4" s="12" t="s">
         <v>79</v>
       </c>
@@ -2107,7 +2124,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:8">
       <c r="A5" s="12" t="s">
         <v>80</v>
       </c>
@@ -2118,7 +2135,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:8">
       <c r="A6" s="12" t="s">
         <v>81</v>
       </c>
@@ -2129,167 +2146,148 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
-      <c r="A7" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="C7" s="4">
-        <v>7000</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9">
+    <row r="7" spans="1:8">
+      <c r="A7" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="B7" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="C7" s="17">
+        <v>188</v>
+      </c>
+      <c r="D7" s="4">
+        <v>288</v>
+      </c>
+      <c r="E7" s="4">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8" s="5" t="s">
         <v>108</v>
       </c>
       <c r="B8" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="C8" s="4">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="B9" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="C8" s="4">
+      <c r="C9" s="4">
         <v>14000</v>
       </c>
     </row>
-    <row r="9" spans="1:9">
-      <c r="A9" s="5" t="s">
+    <row r="10" spans="1:8">
+      <c r="A10" s="5"/>
+      <c r="B10" s="5"/>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="5" t="s">
         <v>109</v>
-      </c>
-      <c r="B9" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="C9" s="4">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9">
-      <c r="A11" s="4" t="s">
-        <v>85</v>
       </c>
       <c r="B11" s="11" t="s">
         <v>89</v>
       </c>
       <c r="C11" s="4">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="C13" s="4">
         <v>1000</v>
       </c>
     </row>
-    <row r="12" spans="1:9">
-      <c r="A12" s="4" t="s">
+    <row r="14" spans="1:8">
+      <c r="A14" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="B12" s="11" t="s">
+      <c r="B14" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="C12" s="4">
+      <c r="C14" s="4">
         <v>1000</v>
       </c>
     </row>
-    <row r="13" spans="1:9">
-      <c r="A13" s="4" t="s">
+    <row r="15" spans="1:8">
+      <c r="A15" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B15" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="C13" s="4">
+      <c r="C15" s="4">
         <v>188</v>
       </c>
-      <c r="D13" s="4">
+      <c r="D15" s="4">
         <v>288</v>
       </c>
-      <c r="E13" s="4">
+      <c r="E15" s="4">
         <v>588</v>
       </c>
-      <c r="F13" s="4">
+      <c r="F15" s="4">
         <v>688</v>
       </c>
-      <c r="G13" s="11">
+      <c r="G15" s="11">
         <v>888</v>
       </c>
-      <c r="H13" s="4">
+      <c r="H15" s="4">
         <v>1888</v>
       </c>
-      <c r="I13" s="4">
-        <v>2888</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9">
-      <c r="A14" s="4" t="s">
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="B14" s="11" t="s">
+      <c r="B16" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="C14" s="4">
+      <c r="C16" s="4">
         <v>300</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D16" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="E14" s="4">
+      <c r="E16" s="4">
         <v>1200</v>
       </c>
     </row>
-    <row r="15" spans="1:9">
-      <c r="A15" s="4" t="s">
+    <row r="17" spans="1:12">
+      <c r="A17" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="B15" s="11" t="s">
+      <c r="B17" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="C15" s="4">
+      <c r="C17" s="4">
         <v>800</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D17" s="4" t="s">
         <v>91</v>
-      </c>
-      <c r="E15" s="4">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9">
-      <c r="A16" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="D16" s="4">
-        <v>1000</v>
-      </c>
-      <c r="E16" s="4">
-        <v>2000</v>
-      </c>
-      <c r="F16" s="4">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8">
-      <c r="A17" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="B17" s="11" t="s">
-        <v>99</v>
-      </c>
-      <c r="D17" s="4">
-        <v>1000</v>
       </c>
       <c r="E17" s="4">
         <v>2000</v>
       </c>
-      <c r="F17" s="4">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8">
+    </row>
+    <row r="18" spans="1:12">
       <c r="A18" s="4" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>96</v>
@@ -2303,32 +2301,107 @@
       <c r="F18" s="4">
         <v>3000</v>
       </c>
-      <c r="G18" s="4">
+    </row>
+    <row r="19" spans="1:12">
+      <c r="A19" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="D19" s="4">
+        <v>1000</v>
+      </c>
+      <c r="E19" s="4">
+        <v>2000</v>
+      </c>
+      <c r="F19" s="4">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12">
+      <c r="A20" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="D20" s="4">
+        <v>1000</v>
+      </c>
+      <c r="E20" s="4">
+        <v>2000</v>
+      </c>
+      <c r="F20" s="4">
+        <v>3000</v>
+      </c>
+      <c r="G20" s="4">
         <v>4000</v>
       </c>
-      <c r="H18" s="11">
+      <c r="H20" s="11">
         <v>5000</v>
       </c>
     </row>
-    <row r="19" spans="1:8">
-      <c r="A19" s="5" t="s">
+    <row r="21" spans="1:12">
+      <c r="A21" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B21" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="C19" s="4">
+      <c r="C21" s="4">
         <v>1000</v>
       </c>
     </row>
-    <row r="20" spans="1:8">
-      <c r="A20" s="5" t="s">
+    <row r="22" spans="1:12">
+      <c r="A22" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B22" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="C20" s="4">
+      <c r="C22" s="4">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12">
+      <c r="A23" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="C23" s="4">
+        <v>100</v>
+      </c>
+      <c r="D23" s="4">
+        <v>200</v>
+      </c>
+      <c r="E23" s="4">
+        <v>300</v>
+      </c>
+      <c r="F23" s="4">
+        <v>400</v>
+      </c>
+      <c r="G23" s="4">
+        <v>500</v>
+      </c>
+      <c r="H23" s="11">
+        <v>600</v>
+      </c>
+      <c r="I23" s="4">
+        <v>700</v>
+      </c>
+      <c r="J23" s="4">
+        <v>800</v>
+      </c>
+      <c r="K23" s="4">
+        <v>900</v>
+      </c>
+      <c r="L23" s="4">
         <v>1000</v>
       </c>
     </row>

--- a/DataTables/剧情大纲.xlsx
+++ b/DataTables/剧情大纲.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{760D911C-C1D2-4507-9B87-E00B9CD90CBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7A3CBE9-F587-4796-A979-AF14165669A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -654,8 +654,204 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <r>
-      <t>每个</t>
+    <t>布匹棉衣</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>奖励金钱</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>奖励名望</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>奖励心得</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>田租</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>俸禄</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>全解</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>锁</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>022</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>023</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>024</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>025</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>元宵灯节</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>主线剧情</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>000</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>004</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>老师心阳虚</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>id</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>心得</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>027</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>上元灯节</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>009</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>027</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>辞别老</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>师</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>金钱</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>名望</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>心得</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>剧情名</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>024</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>王百堂来访</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>药商来访</t>
+  </si>
+  <si>
+    <t>柳敬亭温燥证</t>
+  </si>
+  <si>
+    <t>谢飞燕肺气虚</t>
+  </si>
+  <si>
+    <t>谢飞燕肺阴虚</t>
+  </si>
+  <si>
+    <t>028</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>痰迷心窍</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>秋税</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>夏税</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>大暑</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>霜降</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>医书</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>每个节气</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>病家谢礼</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>妙手回春20%</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>每两个</t>
     </r>
     <r>
       <rPr>
@@ -677,202 +873,6 @@
       </rPr>
       <t>气30%概率</t>
     </r>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>布匹棉衣</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>奖励金钱</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>奖励名望</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>奖励心得</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>田租</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>俸禄</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <r>
-      <t>全解</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>锁</t>
-    </r>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>022</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>023</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>024</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>025</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>026</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>元宵灯节</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>主线剧情</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>000</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>004</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>老师心阳虚</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>id</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>心得</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>027</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>上元灯节</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>009</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>027</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <r>
-      <t>辞别老</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>师</t>
-    </r>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>金钱</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>名望</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>心得</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>剧情名</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>024</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>王百堂来访</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>药商来访</t>
-  </si>
-  <si>
-    <t>柳敬亭温燥证</t>
-  </si>
-  <si>
-    <t>谢飞燕肺气虚</t>
-  </si>
-  <si>
-    <t>谢飞燕肺阴虚</t>
-  </si>
-  <si>
-    <t>028</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>痰迷心窍</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>秋税</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>夏税</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>大暑</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>霜降</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>医书</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>每个节气</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>病家谢礼</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>妙手回春20%</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -966,7 +966,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1004,7 +1004,6 @@
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -1409,13 +1408,13 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="C1" s="8" t="s">
         <v>121</v>
-      </c>
-      <c r="B1" s="8" t="s">
-        <v>131</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>122</v>
       </c>
       <c r="D1" s="8" t="s">
         <v>72</v>
@@ -1424,21 +1423,21 @@
         <v>75</v>
       </c>
       <c r="F1" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="G1" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="H1" s="8" t="s">
         <v>129</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="B2" s="8" t="s">
         <v>119</v>
-      </c>
-      <c r="B2" s="8" t="s">
-        <v>120</v>
       </c>
       <c r="E2" s="9">
         <v>3</v>
@@ -1446,10 +1445,10 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="14" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C3" s="8">
         <v>14</v>
@@ -1457,14 +1456,14 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C4" s="8"/>
       <c r="D4" s="14" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E4" s="9">
         <v>2</v>
@@ -1475,7 +1474,7 @@
         <v>23</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C5" s="8">
         <v>36</v>
@@ -1483,10 +1482,10 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="14" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C6" s="8">
         <v>40</v>
@@ -1494,10 +1493,10 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="14" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C7" s="8">
         <v>44</v>
@@ -1505,10 +1504,10 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="14" t="s">
+        <v>131</v>
+      </c>
+      <c r="B8" s="8" t="s">
         <v>132</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>133</v>
       </c>
       <c r="C8" s="8"/>
       <c r="D8" s="16" t="s">
@@ -1537,10 +1536,10 @@
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="16" t="s">
+        <v>137</v>
+      </c>
+      <c r="B10" s="15" t="s">
         <v>138</v>
-      </c>
-      <c r="B10" s="15" t="s">
-        <v>139</v>
       </c>
       <c r="C10" s="8">
         <v>62</v>
@@ -1570,7 +1569,7 @@
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="14" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B13" s="8" t="s">
         <v>21</v>
@@ -1584,10 +1583,10 @@
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="B14" s="8" t="s">
         <v>123</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>124</v>
       </c>
       <c r="C14" s="8"/>
       <c r="E14" s="9">
@@ -1596,7 +1595,7 @@
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="14" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B15" s="8" t="s">
         <v>22</v>
@@ -1605,7 +1604,7 @@
         <v>105</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E15" s="9">
         <v>1</v>
@@ -1613,14 +1612,14 @@
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="14" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C16" s="8"/>
       <c r="D16" s="14" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E16" s="9">
         <v>2</v>
@@ -1628,7 +1627,7 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="14" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B17" s="8" t="s">
         <v>16</v>
@@ -1684,13 +1683,13 @@
         <v>72</v>
       </c>
       <c r="E1" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>106</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -1760,7 +1759,7 @@
         <v>35</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D6" s="8"/>
       <c r="G6" s="4"/>
@@ -1972,13 +1971,13 @@
         <v>75</v>
       </c>
       <c r="F1" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="G1" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="H1" s="4" t="s">
         <v>106</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -2050,7 +2049,7 @@
     </row>
     <row r="9" spans="1:11">
       <c r="B9" s="8" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K9" s="8"/>
     </row>
@@ -2147,13 +2146,13 @@
       </c>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="17" t="s">
+      <c r="A7" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="B7" s="17" t="s">
-        <v>147</v>
-      </c>
-      <c r="C7" s="17">
+      <c r="C7" s="5">
         <v>188</v>
       </c>
       <c r="D7" s="4">
@@ -2165,10 +2164,10 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C8" s="4">
         <v>7000</v>
@@ -2176,10 +2175,10 @@
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C9" s="4">
         <v>14000</v>
@@ -2191,7 +2190,7 @@
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B11" s="11" t="s">
         <v>89</v>
@@ -2227,7 +2226,7 @@
         <v>102</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>103</v>
+        <v>147</v>
       </c>
       <c r="C15" s="4">
         <v>188</v>
@@ -2267,7 +2266,7 @@
     </row>
     <row r="17" spans="1:12">
       <c r="A17" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B17" s="11" t="s">
         <v>92</v>
@@ -2347,10 +2346,10 @@
     </row>
     <row r="21" spans="1:12">
       <c r="A21" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="B21" s="5" t="s">
         <v>141</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>142</v>
       </c>
       <c r="C21" s="4">
         <v>1000</v>
@@ -2358,10 +2357,10 @@
     </row>
     <row r="22" spans="1:12">
       <c r="A22" s="5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C22" s="4">
         <v>1000</v>
@@ -2369,10 +2368,10 @@
     </row>
     <row r="23" spans="1:12">
       <c r="A23" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="B23" s="5" t="s">
         <v>144</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>145</v>
       </c>
       <c r="C23" s="4">
         <v>100</v>
